--- a/public/samples/ctia-bpr-supplement.xlsx
+++ b/public/samples/ctia-bpr-supplement.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
@@ -32,10 +32,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
+  <numFmts count="12">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="168" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="170" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="171" formatCode="&quot;$&quot;#,##0.0_);[Red]\(&quot;$&quot;#,##0.0\)"/>
+    <numFmt numFmtId="172" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="173" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -399,46 +408,161 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:AL25"/>
+  <cols>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" customWidth="1"/>
+    <col min="17" max="17" width="14.83203125" customWidth="1"/>
+    <col min="18" max="18" width="14.83203125" customWidth="1"/>
+    <col min="19" max="19" width="14.83203125" customWidth="1"/>
+    <col min="20" max="20" width="14.83203125" customWidth="1"/>
+    <col min="21" max="21" width="14.83203125" customWidth="1"/>
+    <col min="22" max="22" width="14.83203125" customWidth="1"/>
+    <col min="23" max="23" width="14.83203125" customWidth="1"/>
+    <col min="24" max="24" width="14.83203125" customWidth="1"/>
+    <col min="25" max="25" width="14.83203125" customWidth="1"/>
+    <col min="26" max="26" width="14.83203125" customWidth="1"/>
+    <col min="27" max="27" width="14.83203125" customWidth="1"/>
+    <col min="28" max="28" width="14.83203125" customWidth="1"/>
+    <col min="29" max="29" width="14.83203125" customWidth="1"/>
+    <col min="30" max="30" width="14.83203125" customWidth="1"/>
+    <col min="31" max="31" width="14.83203125" customWidth="1"/>
+    <col min="32" max="32" width="14.83203125" customWidth="1"/>
+    <col min="33" max="33" width="14.83203125" customWidth="1"/>
+    <col min="34" max="34" width="14.83203125" customWidth="1"/>
+    <col min="35" max="35" width="14.83203125" customWidth="1"/>
+    <col min="36" max="36" width="14.83203125" customWidth="1"/>
+    <col min="37" max="37" width="14.83203125" customWidth="1"/>
+    <col min="38" max="38" width="14.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
+      <c r="A1" t="str">
+        <v/>
+      </c>
       <c r="B1" t="str">
         <v>YTD</v>
       </c>
       <c r="C1" t="str">
+        <v>2024-01</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2024-02</v>
+      </c>
+      <c r="E1" t="str">
+        <v>2024-03</v>
+      </c>
+      <c r="F1" t="str">
+        <v>2024-04</v>
+      </c>
+      <c r="G1" t="str">
+        <v>2024-05</v>
+      </c>
+      <c r="H1" t="str">
+        <v>2024-06</v>
+      </c>
+      <c r="I1" t="str">
+        <v>2024-07</v>
+      </c>
+      <c r="J1" t="str">
+        <v>2024-08</v>
+      </c>
+      <c r="K1" t="str">
+        <v>2024-09</v>
+      </c>
+      <c r="L1" t="str">
+        <v>2024-10</v>
+      </c>
+      <c r="M1" t="str">
+        <v>2024-11</v>
+      </c>
+      <c r="N1" t="str">
+        <v>2024-12</v>
+      </c>
+      <c r="O1" t="str">
+        <v>2025-01</v>
+      </c>
+      <c r="P1" t="str">
+        <v>2025-02</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>2025-03</v>
+      </c>
+      <c r="R1" t="str">
+        <v>2025-04</v>
+      </c>
+      <c r="S1" t="str">
+        <v>2025-05</v>
+      </c>
+      <c r="T1" t="str">
+        <v>2025-06</v>
+      </c>
+      <c r="U1" t="str">
+        <v>2025-07</v>
+      </c>
+      <c r="V1" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="W1" t="str">
+        <v>2025-09</v>
+      </c>
+      <c r="X1" t="str">
+        <v>2025-10</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>2025-11</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>2025-12</v>
+      </c>
+      <c r="AA1" t="str">
         <v>2026-01</v>
       </c>
-      <c r="D1" t="str">
+      <c r="AB1" t="str">
         <v>2026-02</v>
       </c>
-      <c r="E1" t="str">
+      <c r="AC1" t="str">
         <v>2026-03</v>
       </c>
-      <c r="F1" t="str">
+      <c r="AD1" t="str">
         <v>2026-04</v>
       </c>
-      <c r="G1" t="str">
+      <c r="AE1" t="str">
         <v>2026-05</v>
       </c>
-      <c r="H1" t="str">
+      <c r="AF1" t="str">
         <v>2026-06</v>
       </c>
-      <c r="I1" t="str">
+      <c r="AG1" t="str">
         <v>2026-07</v>
       </c>
-      <c r="J1" t="str">
+      <c r="AH1" t="str">
         <v>2026-08</v>
       </c>
-      <c r="K1" t="str">
+      <c r="AI1" t="str">
         <v>2026-09</v>
       </c>
-      <c r="L1" t="str">
+      <c r="AJ1" t="str">
         <v>2026-10</v>
       </c>
-      <c r="M1" t="str">
+      <c r="AK1" t="str">
         <v>2026-11</v>
       </c>
-      <c r="N1" t="str">
+      <c r="AL1" t="str">
         <v>2026-12</v>
       </c>
     </row>
@@ -447,34 +571,100 @@
         <v>验车量</v>
       </c>
       <c r="B2">
-        <v>10400</v>
+        <v>3325</v>
       </c>
       <c r="C2">
-        <v>153</v>
+        <v>790</v>
       </c>
       <c r="D2">
-        <v>166</v>
+        <v>568</v>
       </c>
       <c r="E2">
-        <v>179</v>
+        <v>682</v>
       </c>
       <c r="F2">
-        <v>192</v>
+        <v>728</v>
       </c>
       <c r="G2">
-        <v>108</v>
+        <v>671</v>
       </c>
       <c r="H2">
-        <v>121</v>
+        <v>617</v>
       </c>
       <c r="I2">
-        <v>134</v>
+        <v>580</v>
       </c>
       <c r="J2">
-        <v>147</v>
+        <v>536</v>
       </c>
       <c r="K2">
-        <v>160</v>
+        <v>407</v>
+      </c>
+      <c r="L2">
+        <v>422</v>
+      </c>
+      <c r="M2">
+        <v>484</v>
+      </c>
+      <c r="N2">
+        <v>453</v>
+      </c>
+      <c r="O2">
+        <v>563</v>
+      </c>
+      <c r="P2">
+        <v>640</v>
+      </c>
+      <c r="Q2">
+        <v>695</v>
+      </c>
+      <c r="R2">
+        <v>472</v>
+      </c>
+      <c r="S2">
+        <v>440</v>
+      </c>
+      <c r="T2">
+        <v>537</v>
+      </c>
+      <c r="U2">
+        <v>530</v>
+      </c>
+      <c r="V2">
+        <v>600</v>
+      </c>
+      <c r="W2">
+        <v>347</v>
+      </c>
+      <c r="X2">
+        <v>536</v>
+      </c>
+      <c r="Y2">
+        <v>633</v>
+      </c>
+      <c r="Z2">
+        <v>564</v>
+      </c>
+      <c r="AA2">
+        <v>525</v>
+      </c>
+      <c r="AB2">
+        <v>460</v>
+      </c>
+      <c r="AC2">
+        <v>580</v>
+      </c>
+      <c r="AD2">
+        <v>420</v>
+      </c>
+      <c r="AE2">
+        <v>400</v>
+      </c>
+      <c r="AF2">
+        <v>460</v>
+      </c>
+      <c r="AG2">
+        <v>480</v>
       </c>
     </row>
     <row r="3">
@@ -482,34 +672,100 @@
         <v>咨询量</v>
       </c>
       <c r="B3">
-        <v>10570</v>
+        <v>2439</v>
       </c>
       <c r="C3">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="D3">
-        <v>183</v>
+        <v>57</v>
       </c>
       <c r="E3">
-        <v>196</v>
+        <v>62</v>
       </c>
       <c r="F3">
-        <v>112</v>
+        <v>47</v>
       </c>
       <c r="G3">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="H3">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="I3">
-        <v>151</v>
+        <v>108</v>
       </c>
       <c r="J3">
-        <v>164</v>
+        <v>620</v>
       </c>
       <c r="K3">
-        <v>177</v>
+        <v>582</v>
+      </c>
+      <c r="L3">
+        <v>501</v>
+      </c>
+      <c r="M3">
+        <v>569</v>
+      </c>
+      <c r="N3">
+        <v>505</v>
+      </c>
+      <c r="O3">
+        <v>672</v>
+      </c>
+      <c r="P3">
+        <v>643</v>
+      </c>
+      <c r="Q3">
+        <v>631</v>
+      </c>
+      <c r="R3">
+        <v>478</v>
+      </c>
+      <c r="S3">
+        <v>582</v>
+      </c>
+      <c r="T3">
+        <v>551</v>
+      </c>
+      <c r="U3">
+        <v>484</v>
+      </c>
+      <c r="V3">
+        <v>565</v>
+      </c>
+      <c r="W3">
+        <v>441</v>
+      </c>
+      <c r="X3">
+        <v>554</v>
+      </c>
+      <c r="Y3">
+        <v>579</v>
+      </c>
+      <c r="Z3">
+        <v>620</v>
+      </c>
+      <c r="AA3">
+        <v>640</v>
+      </c>
+      <c r="AB3">
+        <v>237</v>
+      </c>
+      <c r="AC3">
+        <v>253</v>
+      </c>
+      <c r="AD3">
+        <v>305</v>
+      </c>
+      <c r="AE3">
+        <v>356</v>
+      </c>
+      <c r="AF3">
+        <v>327</v>
+      </c>
+      <c r="AG3">
+        <v>321</v>
       </c>
     </row>
     <row r="4">
@@ -517,34 +773,61 @@
         <v>一站式应续保</v>
       </c>
       <c r="B4">
-        <v>174</v>
-      </c>
-      <c r="C4">
-        <v>187</v>
-      </c>
-      <c r="D4">
-        <v>103</v>
-      </c>
-      <c r="E4">
-        <v>116</v>
-      </c>
-      <c r="F4">
-        <v>129</v>
-      </c>
-      <c r="G4">
-        <v>142</v>
-      </c>
-      <c r="H4">
-        <v>155</v>
-      </c>
-      <c r="I4">
-        <v>168</v>
-      </c>
-      <c r="J4">
-        <v>181</v>
-      </c>
-      <c r="K4">
-        <v>194</v>
+        <v>721</v>
+      </c>
+      <c r="R4">
+        <v>20</v>
+      </c>
+      <c r="S4">
+        <v>49</v>
+      </c>
+      <c r="T4">
+        <v>54</v>
+      </c>
+      <c r="U4">
+        <v>79</v>
+      </c>
+      <c r="V4">
+        <v>82</v>
+      </c>
+      <c r="W4">
+        <v>75</v>
+      </c>
+      <c r="X4">
+        <v>73</v>
+      </c>
+      <c r="Y4">
+        <v>80</v>
+      </c>
+      <c r="Z4">
+        <v>70</v>
+      </c>
+      <c r="AA4">
+        <v>92</v>
+      </c>
+      <c r="AB4">
+        <v>91</v>
+      </c>
+      <c r="AC4">
+        <v>101</v>
+      </c>
+      <c r="AD4">
+        <v>64</v>
+      </c>
+      <c r="AE4">
+        <v>63</v>
+      </c>
+      <c r="AF4">
+        <v>70</v>
+      </c>
+      <c r="AG4">
+        <v>80</v>
+      </c>
+      <c r="AH4">
+        <v>84</v>
+      </c>
+      <c r="AI4">
+        <v>76</v>
       </c>
     </row>
     <row r="5">
@@ -552,34 +835,61 @@
         <v>- 一站式應續保已續保</v>
       </c>
       <c r="B5">
-        <v>191</v>
-      </c>
-      <c r="C5">
-        <v>107</v>
-      </c>
-      <c r="D5">
-        <v>120</v>
-      </c>
-      <c r="E5">
-        <v>133</v>
-      </c>
-      <c r="F5">
-        <v>146</v>
-      </c>
-      <c r="G5">
-        <v>159</v>
-      </c>
-      <c r="H5">
-        <v>172</v>
-      </c>
-      <c r="I5">
-        <v>185</v>
-      </c>
-      <c r="J5">
-        <v>101</v>
-      </c>
-      <c r="K5">
-        <v>114</v>
+        <v>279</v>
+      </c>
+      <c r="R5">
+        <v>8</v>
+      </c>
+      <c r="S5">
+        <v>26</v>
+      </c>
+      <c r="T5">
+        <v>28</v>
+      </c>
+      <c r="U5">
+        <v>42</v>
+      </c>
+      <c r="V5">
+        <v>44</v>
+      </c>
+      <c r="W5">
+        <v>39</v>
+      </c>
+      <c r="X5">
+        <v>43</v>
+      </c>
+      <c r="Y5">
+        <v>46</v>
+      </c>
+      <c r="Z5">
+        <v>39</v>
+      </c>
+      <c r="AA5">
+        <v>48</v>
+      </c>
+      <c r="AB5">
+        <v>47</v>
+      </c>
+      <c r="AC5">
+        <v>60</v>
+      </c>
+      <c r="AD5">
+        <v>27</v>
+      </c>
+      <c r="AE5">
+        <v>24</v>
+      </c>
+      <c r="AF5">
+        <v>27</v>
+      </c>
+      <c r="AG5">
+        <v>39</v>
+      </c>
+      <c r="AH5">
+        <v>6</v>
+      </c>
+      <c r="AI5">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -587,34 +897,61 @@
         <v>- 一站式應續保未續保</v>
       </c>
       <c r="B6">
-        <v>111</v>
-      </c>
-      <c r="C6">
-        <v>124</v>
-      </c>
-      <c r="D6">
-        <v>137</v>
-      </c>
-      <c r="E6">
-        <v>150</v>
-      </c>
-      <c r="F6">
-        <v>163</v>
-      </c>
-      <c r="G6">
-        <v>176</v>
-      </c>
-      <c r="H6">
-        <v>189</v>
-      </c>
-      <c r="I6">
-        <v>105</v>
-      </c>
-      <c r="J6">
-        <v>118</v>
-      </c>
-      <c r="K6">
-        <v>131</v>
+        <v>442</v>
+      </c>
+      <c r="R6">
+        <v>12</v>
+      </c>
+      <c r="S6">
+        <v>23</v>
+      </c>
+      <c r="T6">
+        <v>26</v>
+      </c>
+      <c r="U6">
+        <v>37</v>
+      </c>
+      <c r="V6">
+        <v>38</v>
+      </c>
+      <c r="W6">
+        <v>36</v>
+      </c>
+      <c r="X6">
+        <v>30</v>
+      </c>
+      <c r="Y6">
+        <v>34</v>
+      </c>
+      <c r="Z6">
+        <v>31</v>
+      </c>
+      <c r="AA6">
+        <v>44</v>
+      </c>
+      <c r="AB6">
+        <v>44</v>
+      </c>
+      <c r="AC6">
+        <v>41</v>
+      </c>
+      <c r="AD6">
+        <v>37</v>
+      </c>
+      <c r="AE6">
+        <v>39</v>
+      </c>
+      <c r="AF6">
+        <v>43</v>
+      </c>
+      <c r="AG6">
+        <v>41</v>
+      </c>
+      <c r="AH6">
+        <v>78</v>
+      </c>
+      <c r="AI6">
+        <v>75</v>
       </c>
     </row>
     <row r="7">
@@ -622,7 +959,6 @@
         <v>等效先認應續保</v>
       </c>
       <c r="B7">
-        <f>SUM(C7:N7)</f>
         <v>0</v>
       </c>
       <c r="C7">
@@ -650,6 +986,87 @@
         <v>0</v>
       </c>
       <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
         <v>0</v>
       </c>
     </row>
@@ -658,7 +1075,6 @@
         <v>- 等效先認應續保已續保</v>
       </c>
       <c r="B8">
-        <f>SUM(C8:N8)</f>
         <v>0</v>
       </c>
       <c r="C8">
@@ -686,6 +1102,87 @@
         <v>0</v>
       </c>
       <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
         <v>0</v>
       </c>
     </row>
@@ -694,7 +1191,6 @@
         <v>- 等效先認應續保未續保</v>
       </c>
       <c r="B9">
-        <f>SUM(C9:N9)</f>
         <v>0</v>
       </c>
       <c r="C9">
@@ -724,531 +1220,1026 @@
       <c r="K9">
         <v>0</v>
       </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
-      <c r="B10">
-        <f>SUM(C10:N10)</f>
-        <v>0</v>
+      <c r="A10" t="str">
+        <v>SEM Report</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SEM Report</v>
+        <v>- Impression</v>
       </c>
       <c r="B11">
-        <f>SUM(C11:N11)</f>
-        <v>0</v>
+        <v>20926</v>
+      </c>
+      <c r="H11">
+        <v>212</v>
+      </c>
+      <c r="I11">
+        <v>848</v>
+      </c>
+      <c r="J11">
+        <v>1137</v>
+      </c>
+      <c r="K11">
+        <v>1626</v>
+      </c>
+      <c r="L11">
+        <v>1673</v>
+      </c>
+      <c r="M11">
+        <v>1582</v>
+      </c>
+      <c r="N11">
+        <v>1556</v>
+      </c>
+      <c r="O11">
+        <v>2028</v>
+      </c>
+      <c r="P11">
+        <v>2346</v>
+      </c>
+      <c r="Q11">
+        <v>2196</v>
+      </c>
+      <c r="R11">
+        <v>1870</v>
+      </c>
+      <c r="S11">
+        <v>1606</v>
+      </c>
+      <c r="T11">
+        <v>1858</v>
+      </c>
+      <c r="U11">
+        <v>2082</v>
+      </c>
+      <c r="V11">
+        <v>3414</v>
+      </c>
+      <c r="W11">
+        <v>3937</v>
+      </c>
+      <c r="X11">
+        <v>4884</v>
+      </c>
+      <c r="Y11">
+        <v>4116</v>
+      </c>
+      <c r="Z11">
+        <v>3416</v>
+      </c>
+      <c r="AA11">
+        <v>4349</v>
+      </c>
+      <c r="AB11">
+        <v>3177</v>
+      </c>
+      <c r="AC11">
+        <v>3200</v>
+      </c>
+      <c r="AD11">
+        <v>2600</v>
+      </c>
+      <c r="AE11">
+        <v>2200</v>
+      </c>
+      <c r="AF11">
+        <v>2400</v>
+      </c>
+      <c r="AG11">
+        <v>3000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>- Impression</v>
+        <v>- Clicks</v>
       </c>
       <c r="B12">
-        <v>10160</v>
-      </c>
-      <c r="C12">
-        <v>10290</v>
-      </c>
-      <c r="D12">
-        <v>10420</v>
-      </c>
-      <c r="E12">
-        <v>10550</v>
-      </c>
-      <c r="F12">
-        <v>10680</v>
-      </c>
-      <c r="G12">
-        <v>10810</v>
+        <v>1581</v>
       </c>
       <c r="H12">
-        <v>10940</v>
+        <v>32</v>
       </c>
       <c r="I12">
-        <v>10100</v>
+        <v>161</v>
       </c>
       <c r="J12">
-        <v>10230</v>
+        <v>170</v>
       </c>
       <c r="K12">
-        <v>10360</v>
+        <v>266</v>
+      </c>
+      <c r="L12">
+        <v>267</v>
+      </c>
+      <c r="M12">
+        <v>267</v>
+      </c>
+      <c r="N12">
+        <v>230</v>
+      </c>
+      <c r="O12">
+        <v>300</v>
+      </c>
+      <c r="P12">
+        <v>289</v>
+      </c>
+      <c r="Q12">
+        <v>281</v>
+      </c>
+      <c r="R12">
+        <v>229</v>
+      </c>
+      <c r="S12">
+        <v>194</v>
+      </c>
+      <c r="T12">
+        <v>161</v>
+      </c>
+      <c r="U12">
+        <v>198</v>
+      </c>
+      <c r="V12">
+        <v>229</v>
+      </c>
+      <c r="W12">
+        <v>228</v>
+      </c>
+      <c r="X12">
+        <v>341</v>
+      </c>
+      <c r="Y12">
+        <v>325</v>
+      </c>
+      <c r="Z12">
+        <v>308</v>
+      </c>
+      <c r="AA12">
+        <v>331</v>
+      </c>
+      <c r="AB12">
+        <v>230</v>
+      </c>
+      <c r="AC12">
+        <v>260</v>
+      </c>
+      <c r="AD12">
+        <v>220</v>
+      </c>
+      <c r="AE12">
+        <v>190</v>
+      </c>
+      <c r="AF12">
+        <v>160</v>
+      </c>
+      <c r="AG12">
+        <v>190</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>- Clicks</v>
+        <v>- CTR(ClickThrough Rate)</v>
       </c>
       <c r="B13">
-        <v>10330</v>
-      </c>
-      <c r="C13">
-        <v>146</v>
-      </c>
-      <c r="D13">
-        <v>159</v>
-      </c>
-      <c r="E13">
-        <v>172</v>
-      </c>
-      <c r="F13">
-        <v>185</v>
-      </c>
-      <c r="G13">
-        <v>101</v>
+        <v>0.07555194494886744</v>
       </c>
       <c r="H13">
-        <v>114</v>
+        <v>0.153</v>
       </c>
       <c r="I13">
-        <v>127</v>
+        <v>0.1897</v>
       </c>
       <c r="J13">
-        <v>140</v>
+        <v>0.1496</v>
       </c>
       <c r="K13">
-        <v>153</v>
+        <v>0.1636</v>
+      </c>
+      <c r="L13">
+        <v>0.1598</v>
+      </c>
+      <c r="M13">
+        <v>0.1688</v>
+      </c>
+      <c r="N13">
+        <v>0.1478</v>
+      </c>
+      <c r="O13">
+        <v>0.14792899408284024</v>
+      </c>
+      <c r="P13">
+        <v>0.12318840579710146</v>
+      </c>
+      <c r="Q13">
+        <v>0.127959927140255</v>
+      </c>
+      <c r="R13">
+        <v>0.12245989304812835</v>
+      </c>
+      <c r="S13">
+        <v>0.12079701120797011</v>
+      </c>
+      <c r="T13">
+        <v>0.08665231431646932</v>
+      </c>
+      <c r="U13">
+        <v>0.09510086455331412</v>
+      </c>
+      <c r="V13">
+        <v>0.06707674282366725</v>
+      </c>
+      <c r="W13">
+        <v>0.05791211582423165</v>
+      </c>
+      <c r="X13">
+        <v>0.06981981981981981</v>
+      </c>
+      <c r="Y13">
+        <v>0.07896015549076774</v>
+      </c>
+      <c r="Z13">
+        <v>0.09016393442622951</v>
+      </c>
+      <c r="AA13">
+        <v>0.07610945044837894</v>
+      </c>
+      <c r="AB13">
+        <v>0.07239534151715454</v>
+      </c>
+      <c r="AC13">
+        <v>0.08125</v>
+      </c>
+      <c r="AD13">
+        <v>0.08461538461538462</v>
+      </c>
+      <c r="AE13">
+        <v>0.08636363636363636</v>
+      </c>
+      <c r="AF13">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="AG13">
+        <v>0.06333333333333334</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>- CTR(ClickThrough Rate)</v>
+        <v>- Cost</v>
       </c>
       <c r="B14">
-        <v>0.15</v>
-      </c>
-      <c r="C14">
-        <v>0.08</v>
-      </c>
-      <c r="D14">
-        <v>0.21</v>
-      </c>
-      <c r="E14">
-        <v>0.14</v>
-      </c>
-      <c r="F14">
-        <v>0.1</v>
-      </c>
-      <c r="G14">
-        <v>0.23</v>
+        <v>26526</v>
       </c>
       <c r="H14">
-        <v>0.16</v>
+        <v>370</v>
       </c>
       <c r="I14">
-        <v>0.09</v>
+        <v>1868</v>
       </c>
       <c r="J14">
-        <v>0.22</v>
+        <v>2075</v>
       </c>
       <c r="K14">
-        <v>0.15</v>
+        <v>3252</v>
+      </c>
+      <c r="L14">
+        <v>3467</v>
+      </c>
+      <c r="M14">
+        <v>4357</v>
+      </c>
+      <c r="N14">
+        <v>2858</v>
+      </c>
+      <c r="O14">
+        <v>4530</v>
+      </c>
+      <c r="P14">
+        <v>4299</v>
+      </c>
+      <c r="Q14">
+        <v>4224</v>
+      </c>
+      <c r="R14">
+        <v>3533</v>
+      </c>
+      <c r="S14">
+        <v>4210</v>
+      </c>
+      <c r="T14">
+        <v>2785</v>
+      </c>
+      <c r="U14">
+        <v>3943</v>
+      </c>
+      <c r="V14">
+        <v>3147</v>
+      </c>
+      <c r="W14">
+        <v>3484</v>
+      </c>
+      <c r="X14">
+        <v>4919</v>
+      </c>
+      <c r="Y14">
+        <v>4283</v>
+      </c>
+      <c r="Z14">
+        <v>4239</v>
+      </c>
+      <c r="AA14">
+        <v>5451</v>
+      </c>
+      <c r="AB14">
+        <v>3475</v>
+      </c>
+      <c r="AC14">
+        <v>4400</v>
+      </c>
+      <c r="AD14">
+        <v>3600</v>
+      </c>
+      <c r="AE14">
+        <v>3200</v>
+      </c>
+      <c r="AF14">
+        <v>3000</v>
+      </c>
+      <c r="AG14">
+        <v>3400</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>- Cost</v>
+        <v>- CPC(Cost Per Click)</v>
       </c>
       <c r="B15">
-        <v>10670</v>
-      </c>
-      <c r="C15">
-        <v>10800</v>
-      </c>
-      <c r="D15">
-        <v>10930</v>
-      </c>
-      <c r="E15">
-        <v>10090</v>
-      </c>
-      <c r="F15">
-        <v>10220</v>
-      </c>
-      <c r="G15">
-        <v>10350</v>
+        <v>16.77798861480076</v>
       </c>
       <c r="H15">
-        <v>10480</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>10610</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>10740</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>10870</v>
+        <v>2</v>
+      </c>
+      <c r="L15">
+        <v>3</v>
+      </c>
+      <c r="M15">
+        <v>3</v>
+      </c>
+      <c r="N15">
+        <v>2</v>
+      </c>
+      <c r="O15">
+        <v>15.1</v>
+      </c>
+      <c r="P15">
+        <v>14.875432525951558</v>
+      </c>
+      <c r="Q15">
+        <v>15.03202846975089</v>
+      </c>
+      <c r="R15">
+        <v>15.427947598253276</v>
+      </c>
+      <c r="S15">
+        <v>21.701030927835053</v>
+      </c>
+      <c r="T15">
+        <v>17.29813664596273</v>
+      </c>
+      <c r="U15">
+        <v>19.914141414141415</v>
+      </c>
+      <c r="V15">
+        <v>13.74235807860262</v>
+      </c>
+      <c r="W15">
+        <v>15.280701754385966</v>
+      </c>
+      <c r="X15">
+        <v>14.425219941348974</v>
+      </c>
+      <c r="Y15">
+        <v>13.178461538461539</v>
+      </c>
+      <c r="Z15">
+        <v>13.762987012987013</v>
+      </c>
+      <c r="AA15">
+        <v>16.468277945619334</v>
+      </c>
+      <c r="AB15">
+        <v>15.108695652173912</v>
+      </c>
+      <c r="AC15">
+        <v>16.923076923076923</v>
+      </c>
+      <c r="AD15">
+        <v>16.363636363636363</v>
+      </c>
+      <c r="AE15">
+        <v>16.842105263157894</v>
+      </c>
+      <c r="AF15">
+        <v>18.75</v>
+      </c>
+      <c r="AG15">
+        <v>17.894736842105264</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>- CPC(Cost Per Click)</v>
+        <v>-Coversion</v>
       </c>
       <c r="B16">
+        <v>79</v>
+      </c>
+      <c r="I16">
+        <v>9</v>
+      </c>
+      <c r="J16">
+        <v>11</v>
+      </c>
+      <c r="K16">
+        <v>20</v>
+      </c>
+      <c r="L16">
+        <v>19</v>
+      </c>
+      <c r="M16">
+        <v>15</v>
+      </c>
+      <c r="N16">
+        <v>11</v>
+      </c>
+      <c r="O16">
+        <v>34</v>
+      </c>
+      <c r="P16">
+        <v>24</v>
+      </c>
+      <c r="Q16">
+        <v>22</v>
+      </c>
+      <c r="R16">
         <v>14</v>
       </c>
-      <c r="C16">
+      <c r="S16">
+        <v>14</v>
+      </c>
+      <c r="T16">
+        <v>8</v>
+      </c>
+      <c r="U16">
+        <v>11</v>
+      </c>
+      <c r="V16">
+        <v>12</v>
+      </c>
+      <c r="W16">
+        <v>9</v>
+      </c>
+      <c r="X16">
+        <v>15</v>
+      </c>
+      <c r="Y16">
+        <v>18</v>
+      </c>
+      <c r="Z16">
+        <v>19</v>
+      </c>
+      <c r="AA16">
+        <v>20</v>
+      </c>
+      <c r="AB16">
+        <v>6</v>
+      </c>
+      <c r="AC16">
+        <v>16</v>
+      </c>
+      <c r="AD16">
+        <v>11</v>
+      </c>
+      <c r="AE16">
         <v>10</v>
       </c>
-      <c r="D16">
-        <v>23</v>
-      </c>
-      <c r="E16">
-        <v>36</v>
-      </c>
-      <c r="F16">
-        <v>49</v>
-      </c>
-      <c r="G16">
-        <v>62</v>
-      </c>
-      <c r="H16">
-        <v>75</v>
-      </c>
-      <c r="I16">
-        <v>88</v>
-      </c>
-      <c r="J16">
-        <v>21</v>
-      </c>
-      <c r="K16">
-        <v>17</v>
+      <c r="AF16">
+        <v>7</v>
+      </c>
+      <c r="AG16">
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>-Coversion</v>
+        <v>-CPA(Cost Per Acquisition)</v>
       </c>
       <c r="B17">
-        <v>104</v>
-      </c>
-      <c r="C17">
-        <v>27</v>
-      </c>
-      <c r="D17">
-        <v>40</v>
-      </c>
-      <c r="E17">
-        <v>53</v>
-      </c>
-      <c r="F17">
-        <v>66</v>
-      </c>
-      <c r="G17">
-        <v>79</v>
-      </c>
-      <c r="H17">
-        <v>12</v>
+        <v>335.7721518987342</v>
       </c>
       <c r="I17">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="J17">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="K17">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="L17">
+        <v>36</v>
+      </c>
+      <c r="M17">
+        <v>60</v>
+      </c>
+      <c r="N17">
+        <v>54</v>
+      </c>
+      <c r="O17">
+        <v>133.23529411764707</v>
+      </c>
+      <c r="P17">
+        <v>179.125</v>
+      </c>
+      <c r="Q17">
+        <v>192</v>
+      </c>
+      <c r="R17">
+        <v>252.35714285714286</v>
+      </c>
+      <c r="S17">
+        <v>300.7142857142857</v>
+      </c>
+      <c r="T17">
+        <v>348.125</v>
+      </c>
+      <c r="U17">
+        <v>358.45454545454544</v>
+      </c>
+      <c r="V17">
+        <v>262.25</v>
+      </c>
+      <c r="W17">
+        <v>387.1111111111111</v>
+      </c>
+      <c r="X17">
+        <v>327.93333333333334</v>
+      </c>
+      <c r="Y17">
+        <v>237.94444444444446</v>
+      </c>
+      <c r="Z17">
+        <v>223.10526315789474</v>
+      </c>
+      <c r="AA17">
+        <v>272.55</v>
+      </c>
+      <c r="AB17">
+        <v>579.1666666666666</v>
+      </c>
+      <c r="AC17">
+        <v>275</v>
+      </c>
+      <c r="AD17">
+        <v>327.27272727272725</v>
+      </c>
+      <c r="AE17">
+        <v>320</v>
+      </c>
+      <c r="AF17">
+        <v>428.57142857142856</v>
+      </c>
+      <c r="AG17">
+        <v>377.77777777777777</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>-CPA(Cost Per Acquisition)</v>
-      </c>
-      <c r="B18">
-        <v>121</v>
-      </c>
-      <c r="C18">
-        <v>134</v>
-      </c>
-      <c r="D18">
-        <v>147</v>
-      </c>
-      <c r="E18">
-        <v>160</v>
-      </c>
-      <c r="F18">
-        <v>173</v>
-      </c>
-      <c r="G18">
-        <v>186</v>
-      </c>
-      <c r="H18">
-        <v>102</v>
-      </c>
-      <c r="I18">
-        <v>115</v>
-      </c>
-      <c r="J18">
-        <v>128</v>
-      </c>
-      <c r="K18">
-        <v>141</v>
+        <v>FB Report</v>
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="str">
+        <v>- Impression</v>
+      </c>
       <c r="B19">
-        <f>SUM(C19:N19)</f>
-        <v>0</v>
+        <v>268146</v>
+      </c>
+      <c r="U19">
+        <v>29244</v>
+      </c>
+      <c r="V19">
+        <v>10420</v>
+      </c>
+      <c r="W19">
+        <v>37195</v>
+      </c>
+      <c r="X19">
+        <v>55035</v>
+      </c>
+      <c r="Y19">
+        <v>47745</v>
+      </c>
+      <c r="Z19">
+        <v>53471</v>
+      </c>
+      <c r="AA19">
+        <v>45247</v>
+      </c>
+      <c r="AB19">
+        <v>42899</v>
+      </c>
+      <c r="AC19">
+        <v>40000</v>
+      </c>
+      <c r="AD19">
+        <v>38000</v>
+      </c>
+      <c r="AE19">
+        <v>36000</v>
+      </c>
+      <c r="AF19">
+        <v>34000</v>
+      </c>
+      <c r="AG19">
+        <v>32000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>FB Report</v>
+        <v>- Clicks</v>
       </c>
       <c r="B20">
-        <f>SUM(C20:N20)</f>
-        <v>0</v>
+        <v>2655</v>
+      </c>
+      <c r="U20">
+        <v>280</v>
+      </c>
+      <c r="V20">
+        <v>149</v>
+      </c>
+      <c r="W20">
+        <v>935</v>
+      </c>
+      <c r="X20">
+        <v>621</v>
+      </c>
+      <c r="Y20">
+        <v>549</v>
+      </c>
+      <c r="Z20">
+        <v>570</v>
+      </c>
+      <c r="AA20">
+        <v>559</v>
+      </c>
+      <c r="AB20">
+        <v>296</v>
+      </c>
+      <c r="AC20">
+        <v>400</v>
+      </c>
+      <c r="AD20">
+        <v>380</v>
+      </c>
+      <c r="AE20">
+        <v>360</v>
+      </c>
+      <c r="AF20">
+        <v>340</v>
+      </c>
+      <c r="AG20">
+        <v>320</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>- Impression</v>
+        <v>- CTR(ClickThrough Rate)</v>
       </c>
       <c r="B21">
-        <v>10720</v>
-      </c>
-      <c r="C21">
-        <v>10850</v>
-      </c>
-      <c r="D21">
-        <v>10010</v>
-      </c>
-      <c r="E21">
-        <v>10140</v>
-      </c>
-      <c r="F21">
-        <v>10270</v>
-      </c>
-      <c r="G21">
-        <v>10400</v>
-      </c>
-      <c r="H21">
-        <v>10530</v>
-      </c>
-      <c r="I21">
-        <v>10660</v>
-      </c>
-      <c r="J21">
-        <v>10790</v>
-      </c>
-      <c r="K21">
-        <v>10920</v>
+        <v>0.00990132241390884</v>
+      </c>
+      <c r="U21">
+        <v>0.009574613595951307</v>
+      </c>
+      <c r="V21">
+        <v>0.014299424184261037</v>
+      </c>
+      <c r="W21">
+        <v>0.025137787337007663</v>
+      </c>
+      <c r="X21">
+        <v>0.011283728536385935</v>
+      </c>
+      <c r="Y21">
+        <v>0.011498586239396796</v>
+      </c>
+      <c r="Z21">
+        <v>0.010659983916515495</v>
+      </c>
+      <c r="AA21">
+        <v>0.012354410237142795</v>
+      </c>
+      <c r="AB21">
+        <v>0.006899927737243293</v>
+      </c>
+      <c r="AC21">
+        <v>0.01</v>
+      </c>
+      <c r="AD21">
+        <v>0.01</v>
+      </c>
+      <c r="AE21">
+        <v>0.01</v>
+      </c>
+      <c r="AF21">
+        <v>0.01</v>
+      </c>
+      <c r="AG21">
+        <v>0.01</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>- Clicks</v>
+        <v>- Cost</v>
       </c>
       <c r="B22">
-        <v>10890</v>
-      </c>
-      <c r="C22">
-        <v>105</v>
-      </c>
-      <c r="D22">
-        <v>118</v>
-      </c>
-      <c r="E22">
-        <v>131</v>
-      </c>
-      <c r="F22">
-        <v>144</v>
-      </c>
-      <c r="G22">
-        <v>157</v>
-      </c>
-      <c r="H22">
-        <v>170</v>
-      </c>
-      <c r="I22">
-        <v>183</v>
-      </c>
-      <c r="J22">
-        <v>196</v>
-      </c>
-      <c r="K22">
-        <v>112</v>
+        <v>13684</v>
+      </c>
+      <c r="U22">
+        <v>1759</v>
+      </c>
+      <c r="V22">
+        <v>743</v>
+      </c>
+      <c r="W22">
+        <v>2101</v>
+      </c>
+      <c r="X22">
+        <v>2048</v>
+      </c>
+      <c r="Y22">
+        <v>1952</v>
+      </c>
+      <c r="Z22">
+        <v>2010</v>
+      </c>
+      <c r="AA22">
+        <v>1989</v>
+      </c>
+      <c r="AB22">
+        <v>2035</v>
+      </c>
+      <c r="AC22">
+        <v>2000</v>
+      </c>
+      <c r="AD22">
+        <v>1960</v>
+      </c>
+      <c r="AE22">
+        <v>1920</v>
+      </c>
+      <c r="AF22">
+        <v>1900</v>
+      </c>
+      <c r="AG22">
+        <v>1880</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>- CTR(ClickThrough Rate)</v>
+        <v>- CPC(Cost Per Click)</v>
       </c>
       <c r="B23">
-        <v>0.14</v>
-      </c>
-      <c r="C23">
-        <v>0.07</v>
-      </c>
-      <c r="D23">
-        <v>0.2</v>
-      </c>
-      <c r="E23">
-        <v>0.13</v>
-      </c>
-      <c r="F23">
-        <v>0.06</v>
-      </c>
-      <c r="G23">
-        <v>0.19</v>
-      </c>
-      <c r="H23">
-        <v>0.12</v>
-      </c>
-      <c r="I23">
-        <v>0.08</v>
-      </c>
-      <c r="J23">
-        <v>0.21</v>
-      </c>
-      <c r="K23">
-        <v>0.14</v>
+        <v>5.154048964218456</v>
+      </c>
+      <c r="U23">
+        <v>6.2821428571428575</v>
+      </c>
+      <c r="V23">
+        <v>4.9865771812080535</v>
+      </c>
+      <c r="W23">
+        <v>2.2470588235294118</v>
+      </c>
+      <c r="X23">
+        <v>3.2979066022544283</v>
+      </c>
+      <c r="Y23">
+        <v>3.5555555555555554</v>
+      </c>
+      <c r="Z23">
+        <v>3.526315789473684</v>
+      </c>
+      <c r="AA23">
+        <v>3.558139534883721</v>
+      </c>
+      <c r="AB23">
+        <v>6.875</v>
+      </c>
+      <c r="AC23">
+        <v>5</v>
+      </c>
+      <c r="AD23">
+        <v>5.157894736842105</v>
+      </c>
+      <c r="AE23">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="AF23">
+        <v>5.588235294117647</v>
+      </c>
+      <c r="AG23">
+        <v>5.875</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>- Cost</v>
+        <v>-Coversion</v>
       </c>
       <c r="B24">
-        <v>10260</v>
-      </c>
-      <c r="C24">
-        <v>139</v>
-      </c>
-      <c r="D24">
-        <v>10520</v>
-      </c>
-      <c r="E24">
-        <v>10650</v>
-      </c>
-      <c r="F24">
-        <v>178</v>
-      </c>
-      <c r="G24">
-        <v>191</v>
-      </c>
-      <c r="H24">
-        <v>107</v>
-      </c>
-      <c r="I24">
-        <v>120</v>
-      </c>
-      <c r="J24">
-        <v>133</v>
-      </c>
-      <c r="K24">
-        <v>10460</v>
+        <v>127</v>
+      </c>
+      <c r="U24">
+        <v>4</v>
+      </c>
+      <c r="V24">
+        <v>2</v>
+      </c>
+      <c r="W24">
+        <v>5</v>
+      </c>
+      <c r="X24">
+        <v>17</v>
+      </c>
+      <c r="Y24">
+        <v>12</v>
+      </c>
+      <c r="Z24">
+        <v>15</v>
+      </c>
+      <c r="AA24">
+        <v>15</v>
+      </c>
+      <c r="AB24">
+        <v>32</v>
+      </c>
+      <c r="AC24">
+        <v>20</v>
+      </c>
+      <c r="AD24">
+        <v>18</v>
+      </c>
+      <c r="AE24">
+        <v>16</v>
+      </c>
+      <c r="AF24">
+        <v>14</v>
+      </c>
+      <c r="AG24">
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>- CPC(Cost Per Click)</v>
+        <v>-CPA(Cost Per Acquisition)</v>
       </c>
       <c r="B25">
-        <v>53</v>
-      </c>
-      <c r="C25">
-        <v>66</v>
-      </c>
-      <c r="D25">
-        <v>79</v>
-      </c>
-      <c r="E25">
-        <v>12</v>
-      </c>
-      <c r="F25">
-        <v>25</v>
-      </c>
-      <c r="G25">
-        <v>21</v>
-      </c>
-      <c r="H25">
-        <v>34</v>
-      </c>
-      <c r="I25">
-        <v>47</v>
-      </c>
-      <c r="J25">
-        <v>60</v>
-      </c>
-      <c r="K25">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>-Coversion</v>
-      </c>
-      <c r="B26">
-        <v>160</v>
-      </c>
-      <c r="C26">
-        <v>83</v>
-      </c>
-      <c r="D26">
-        <v>186</v>
-      </c>
-      <c r="E26">
-        <v>102</v>
-      </c>
-      <c r="F26">
-        <v>25</v>
-      </c>
-      <c r="G26">
-        <v>38</v>
-      </c>
-      <c r="H26">
-        <v>51</v>
-      </c>
-      <c r="I26">
-        <v>64</v>
-      </c>
-      <c r="J26">
-        <v>77</v>
-      </c>
-      <c r="K26">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>-CPA(Cost Per Acquisition)</v>
-      </c>
-      <c r="B27">
-        <v>177</v>
-      </c>
-      <c r="C27">
-        <v>190</v>
-      </c>
-      <c r="D27">
-        <v>16</v>
-      </c>
-      <c r="E27">
-        <v>119</v>
-      </c>
-      <c r="F27">
-        <v>132</v>
-      </c>
-      <c r="G27">
-        <v>145</v>
-      </c>
-      <c r="H27">
-        <v>158</v>
-      </c>
-      <c r="I27">
-        <v>171</v>
-      </c>
-      <c r="J27">
-        <v>184</v>
-      </c>
-      <c r="K27">
+        <v>107.74803149606299</v>
+      </c>
+      <c r="U25">
+        <v>439.75</v>
+      </c>
+      <c r="V25">
+        <v>371.5</v>
+      </c>
+      <c r="W25">
+        <v>420.2</v>
+      </c>
+      <c r="X25">
+        <v>120.47058823529412</v>
+      </c>
+      <c r="Y25">
+        <v>162.66666666666666</v>
+      </c>
+      <c r="Z25">
+        <v>134</v>
+      </c>
+      <c r="AA25">
+        <v>132.6</v>
+      </c>
+      <c r="AB25">
+        <v>63.59375</v>
+      </c>
+      <c r="AC25">
         <v>100</v>
       </c>
+      <c r="AD25">
+        <v>108.88888888888889</v>
+      </c>
+      <c r="AE25">
+        <v>120</v>
+      </c>
+      <c r="AF25">
+        <v>135.71428571428572</v>
+      </c>
+      <c r="AG25">
+        <v>156.66666666666666</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL25"/>
   </ignoredErrors>
 </worksheet>
 </file>